--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.147.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.147.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0147.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0147.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -595,18 +595,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Such last mentioned writ of subpo Ã¦ na is to be in the</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: motion :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]140</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]140</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L21: isolated marker/symbol line :: 140</t>
@@ -614,7 +614,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 7</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]140</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,16 +662,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the form :â€” : :</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the form :â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -679,7 +671,11 @@
           <t>L41: isolated marker/symbol line :: 1</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L125: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
@@ -717,16 +713,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served with a writ of subpo Ã¦ ena therein; therefore we com-</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following memorandum to be placed at foot :â€”-</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
@@ -754,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -768,16 +756,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”, in the County of</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to whom the cause stands referred] in the City of â€”â€”</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
@@ -819,16 +799,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: The persons served with such last mentioned subpa Ã¦ ena</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”, in the County of - ---------------------------); and, if you neglect</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -836,7 +808,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”, in the County of - ---------------------------); and, if you neglect</t>
+          <t>L110: punctuation artifact: double/multiple hyphen :: —, in the County of - ---------------------------); and, if you neglect</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -871,11 +843,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Masterâ€™s office, having appeared are to be at liberty to attend, and to be</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -977,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1021,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1060,7 +1028,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
